--- a/jyx2/Assets/Mods/jshyl/Configs/人物.xlsx
+++ b/jyx2/Assets/Mods/jshyl/Configs/人物.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="494">
   <si>
     <t>Id</t>
   </si>
@@ -1530,6 +1530,18 @@
   <si>
     <t>8,13|12,11|22,10</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿青</t>
+  </si>
+  <si>
+    <t>越女剑</t>
+  </si>
+  <si>
+    <t>61,500</t>
+  </si>
+  <si>
+    <t>2,2|3,2</t>
   </si>
 </sst>
 </file>
@@ -1998,16 +2010,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AP324"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AP325"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" ns3:dyDescent="0.25"/>
   <cols>
     <col min="6" max="39" width="9" customWidth="1"/>
     <col min="40" max="40" width="41.08984375" style="1" customWidth="1"/>
     <col min="41" max="41" width="22.7265625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" ns3:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>486</v>
       </c>
@@ -2015,7 +2027,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" ns3:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
@@ -2143,7 +2155,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" ns3:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>482</v>
       </c>
@@ -2257,7 +2269,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" ns3:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -2355,7 +2367,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" ns3:dyDescent="0.25">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -2480,7 +2492,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" ns3:dyDescent="0.25">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -2608,7 +2620,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" ns3:dyDescent="0.25">
       <c r="A7" s="2">
         <v>2</v>
       </c>
@@ -2736,7 +2748,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" ns3:dyDescent="0.25">
       <c r="A8" s="2">
         <v>3</v>
       </c>
@@ -2861,7 +2873,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" ns3:dyDescent="0.25">
       <c r="A9" s="2">
         <v>4</v>
       </c>
@@ -2986,7 +2998,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" ns3:dyDescent="0.25">
       <c r="A10" s="2">
         <v>5</v>
       </c>
@@ -3111,7 +3123,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" ns3:dyDescent="0.25">
       <c r="A11" s="2">
         <v>6</v>
       </c>
@@ -3236,7 +3248,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" ns3:dyDescent="0.25">
       <c r="A12" s="2">
         <v>7</v>
       </c>
@@ -3361,7 +3373,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" ns3:dyDescent="0.25">
       <c r="A13" s="2">
         <v>8</v>
       </c>
@@ -3486,7 +3498,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" ns3:dyDescent="0.25">
       <c r="A14" s="2">
         <v>9</v>
       </c>
@@ -3614,7 +3626,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" ns3:dyDescent="0.25">
       <c r="A15" s="2">
         <v>10</v>
       </c>
@@ -3739,7 +3751,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" ns3:dyDescent="0.25">
       <c r="A16" s="2">
         <v>11</v>
       </c>
@@ -3864,7 +3876,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" ns3:dyDescent="0.25">
       <c r="A17" s="2">
         <v>12</v>
       </c>
@@ -3989,7 +4001,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" ns3:dyDescent="0.25">
       <c r="A18" s="2">
         <v>13</v>
       </c>
@@ -4114,7 +4126,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" ns3:dyDescent="0.25">
       <c r="A19" s="2">
         <v>14</v>
       </c>
@@ -4239,7 +4251,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" ns3:dyDescent="0.25">
       <c r="A20" s="2">
         <v>15</v>
       </c>
@@ -4364,7 +4376,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" ns3:dyDescent="0.25">
       <c r="A21" s="2">
         <v>16</v>
       </c>
@@ -4492,7 +4504,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" ns3:dyDescent="0.25">
       <c r="A22" s="2">
         <v>17</v>
       </c>
@@ -4620,7 +4632,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" ns3:dyDescent="0.25">
       <c r="A23" s="2">
         <v>18</v>
       </c>
@@ -4745,7 +4757,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" ns3:dyDescent="0.25">
       <c r="A24" s="2">
         <v>19</v>
       </c>
@@ -4870,7 +4882,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" ns3:dyDescent="0.25">
       <c r="A25" s="2">
         <v>20</v>
       </c>
@@ -4995,7 +5007,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" ns3:dyDescent="0.25">
       <c r="A26" s="2">
         <v>21</v>
       </c>
@@ -5120,7 +5132,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" ns3:dyDescent="0.25">
       <c r="A27" s="2">
         <v>22</v>
       </c>
@@ -5245,7 +5257,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" ns3:dyDescent="0.25">
       <c r="A28" s="2">
         <v>23</v>
       </c>
@@ -5370,7 +5382,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" ns3:dyDescent="0.25">
       <c r="A29" s="2">
         <v>24</v>
       </c>
@@ -5495,7 +5507,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" ns3:dyDescent="0.25">
       <c r="A30" s="2">
         <v>25</v>
       </c>
@@ -5623,7 +5635,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" ns3:dyDescent="0.25">
       <c r="A31" s="2">
         <v>26</v>
       </c>
@@ -5748,7 +5760,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" ns3:dyDescent="0.25">
       <c r="A32" s="2">
         <v>27</v>
       </c>
@@ -5873,7 +5885,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:42" ns3:dyDescent="0.25">
       <c r="A33" s="2">
         <v>28</v>
       </c>
@@ -6001,7 +6013,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:42" ns3:dyDescent="0.25">
       <c r="A34" s="2">
         <v>29</v>
       </c>
@@ -6129,7 +6141,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:42" ns3:dyDescent="0.25">
       <c r="A35" s="2">
         <v>30</v>
       </c>
@@ -6254,7 +6266,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:42" ns3:dyDescent="0.25">
       <c r="A36" s="2">
         <v>31</v>
       </c>
@@ -6379,7 +6391,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:42" ns3:dyDescent="0.25">
       <c r="A37" s="2">
         <v>32</v>
       </c>
@@ -6504,7 +6516,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:42" ns3:dyDescent="0.25">
       <c r="A38" s="2">
         <v>33</v>
       </c>
@@ -6629,7 +6641,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:42" ns3:dyDescent="0.25">
       <c r="A39" s="2">
         <v>34</v>
       </c>
@@ -6754,7 +6766,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:42" ns3:dyDescent="0.25">
       <c r="A40" s="2">
         <v>35</v>
       </c>
@@ -6882,7 +6894,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:42" ns3:dyDescent="0.25">
       <c r="A41" s="2">
         <v>36</v>
       </c>
@@ -7010,7 +7022,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:42" ns3:dyDescent="0.25">
       <c r="A42" s="2">
         <v>37</v>
       </c>
@@ -7138,7 +7150,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:42" ns3:dyDescent="0.25">
       <c r="A43" s="2">
         <v>38</v>
       </c>
@@ -7266,7 +7278,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:42" ns3:dyDescent="0.25">
       <c r="A44" s="2">
         <v>39</v>
       </c>
@@ -7391,7 +7403,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:42" ns3:dyDescent="0.25">
       <c r="A45" s="2">
         <v>40</v>
       </c>
@@ -7516,7 +7528,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="46" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:42" ns3:dyDescent="0.25">
       <c r="A46" s="2">
         <v>41</v>
       </c>
@@ -7641,7 +7653,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:42" ns3:dyDescent="0.25">
       <c r="A47" s="2">
         <v>42</v>
       </c>
@@ -7766,7 +7778,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="48" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:42" ns3:dyDescent="0.25">
       <c r="A48" s="2">
         <v>43</v>
       </c>
@@ -7891,7 +7903,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="49" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:42" ns3:dyDescent="0.25">
       <c r="A49" s="2">
         <v>44</v>
       </c>
@@ -8019,7 +8031,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="50" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:42" ns3:dyDescent="0.25">
       <c r="A50" s="2">
         <v>45</v>
       </c>
@@ -8147,7 +8159,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="51" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:42" ns3:dyDescent="0.25">
       <c r="A51" s="2">
         <v>46</v>
       </c>
@@ -8272,7 +8284,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="52" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:42" ns3:dyDescent="0.25">
       <c r="A52" s="2">
         <v>47</v>
       </c>
@@ -8400,7 +8412,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="53" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:42" ns3:dyDescent="0.25">
       <c r="A53" s="2">
         <v>48</v>
       </c>
@@ -8528,7 +8540,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="54" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:42" ns3:dyDescent="0.25">
       <c r="A54" s="2">
         <v>49</v>
       </c>
@@ -8656,7 +8668,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="55" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:42" ns3:dyDescent="0.25">
       <c r="A55" s="2">
         <v>50</v>
       </c>
@@ -8781,7 +8793,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:42" ns3:dyDescent="0.25">
       <c r="A56" s="2">
         <v>51</v>
       </c>
@@ -8909,7 +8921,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="57" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:42" ns3:dyDescent="0.25">
       <c r="A57" s="2">
         <v>52</v>
       </c>
@@ -9034,7 +9046,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="58" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:42" ns3:dyDescent="0.25">
       <c r="A58" s="2">
         <v>53</v>
       </c>
@@ -9162,7 +9174,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="59" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:42" ns3:dyDescent="0.25">
       <c r="A59" s="2">
         <v>54</v>
       </c>
@@ -9290,7 +9302,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="60" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:42" ns3:dyDescent="0.25">
       <c r="A60" s="2">
         <v>55</v>
       </c>
@@ -9415,7 +9427,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="61" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:42" ns3:dyDescent="0.25">
       <c r="A61" s="2">
         <v>56</v>
       </c>
@@ -9540,7 +9552,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:42" ns3:dyDescent="0.25">
       <c r="A62" s="2">
         <v>57</v>
       </c>
@@ -9665,7 +9677,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="63" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:42" ns3:dyDescent="0.25">
       <c r="A63" s="2">
         <v>58</v>
       </c>
@@ -9793,7 +9805,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:42" ns3:dyDescent="0.25">
       <c r="A64" s="2">
         <v>59</v>
       </c>
@@ -9921,7 +9933,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="65" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:42" ns3:dyDescent="0.25">
       <c r="A65" s="2">
         <v>60</v>
       </c>
@@ -10046,7 +10058,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="66" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:42" ns3:dyDescent="0.25">
       <c r="A66" s="2">
         <v>61</v>
       </c>
@@ -10174,7 +10186,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="67" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:42" ns3:dyDescent="0.25">
       <c r="A67" s="2">
         <v>62</v>
       </c>
@@ -10299,7 +10311,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="68" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:42" ns3:dyDescent="0.25">
       <c r="A68" s="2">
         <v>63</v>
       </c>
@@ -10427,7 +10439,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="69" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:42" ns3:dyDescent="0.25">
       <c r="A69" s="2">
         <v>64</v>
       </c>
@@ -10552,7 +10564,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="70" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:42" ns3:dyDescent="0.25">
       <c r="A70" s="2">
         <v>65</v>
       </c>
@@ -10677,7 +10689,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="71" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:42" ns3:dyDescent="0.25">
       <c r="A71" s="2">
         <v>66</v>
       </c>
@@ -10802,7 +10814,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="72" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:42" ns3:dyDescent="0.25">
       <c r="A72" s="2">
         <v>67</v>
       </c>
@@ -10927,7 +10939,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="73" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:42" ns3:dyDescent="0.25">
       <c r="A73" s="2">
         <v>68</v>
       </c>
@@ -11052,7 +11064,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="74" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:42" ns3:dyDescent="0.25">
       <c r="A74" s="2">
         <v>69</v>
       </c>
@@ -11177,7 +11189,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="75" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:42" ns3:dyDescent="0.25">
       <c r="A75" s="2">
         <v>70</v>
       </c>
@@ -11302,7 +11314,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="76" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:42" ns3:dyDescent="0.25">
       <c r="A76" s="2">
         <v>71</v>
       </c>
@@ -11427,7 +11439,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="77" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:42" ns3:dyDescent="0.25">
       <c r="A77" s="2">
         <v>72</v>
       </c>
@@ -11552,7 +11564,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="78" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:42" ns3:dyDescent="0.25">
       <c r="A78" s="2">
         <v>73</v>
       </c>
@@ -11677,7 +11689,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="79" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:42" ns3:dyDescent="0.25">
       <c r="A79" s="2">
         <v>74</v>
       </c>
@@ -11802,7 +11814,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="80" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:42" ns3:dyDescent="0.25">
       <c r="A80" s="2">
         <v>75</v>
       </c>
@@ -11927,7 +11939,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="81" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:42" ns3:dyDescent="0.25">
       <c r="A81" s="2">
         <v>76</v>
       </c>
@@ -12055,7 +12067,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="82" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:42" ns3:dyDescent="0.25">
       <c r="A82" s="2">
         <v>77</v>
       </c>
@@ -12180,7 +12192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="83" spans="1:42" ht="14.5" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:42" ht="14.5" ns3:dyDescent="0.4">
       <c r="A83" s="2">
         <v>78</v>
       </c>
@@ -12305,7 +12317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="84" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:42" ns3:dyDescent="0.25">
       <c r="A84" s="2">
         <v>79</v>
       </c>
@@ -12430,7 +12442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="85" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:42" ns3:dyDescent="0.25">
       <c r="A85" s="2">
         <v>80</v>
       </c>
@@ -12555,7 +12567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="86" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:42" ns3:dyDescent="0.25">
       <c r="A86" s="2">
         <v>81</v>
       </c>
@@ -12680,7 +12692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="87" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:42" ns3:dyDescent="0.25">
       <c r="A87" s="2">
         <v>82</v>
       </c>
@@ -12805,7 +12817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="88" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:42" ns3:dyDescent="0.25">
       <c r="A88" s="2">
         <v>83</v>
       </c>
@@ -12930,7 +12942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="89" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:42" ns3:dyDescent="0.25">
       <c r="A89" s="2">
         <v>84</v>
       </c>
@@ -13055,7 +13067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="90" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:42" ns3:dyDescent="0.25">
       <c r="A90" s="2">
         <v>85</v>
       </c>
@@ -13180,7 +13192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="91" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:42" ns3:dyDescent="0.25">
       <c r="A91" s="2">
         <v>86</v>
       </c>
@@ -13305,7 +13317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="92" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:42" ns3:dyDescent="0.25">
       <c r="A92" s="2">
         <v>87</v>
       </c>
@@ -13430,7 +13442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="93" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:42" ns3:dyDescent="0.25">
       <c r="A93" s="2">
         <v>88</v>
       </c>
@@ -13555,7 +13567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="94" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:42" ns3:dyDescent="0.25">
       <c r="A94" s="2">
         <v>89</v>
       </c>
@@ -13680,7 +13692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="95" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:42" ns3:dyDescent="0.25">
       <c r="A95" s="2">
         <v>90</v>
       </c>
@@ -13805,7 +13817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="96" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:42" ns3:dyDescent="0.25">
       <c r="A96" s="2">
         <v>91</v>
       </c>
@@ -13930,7 +13942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="97" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:41" ns3:dyDescent="0.25">
       <c r="A97" s="2">
         <v>92</v>
       </c>
@@ -14055,7 +14067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="98" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:41" ns3:dyDescent="0.25">
       <c r="A98" s="2">
         <v>93</v>
       </c>
@@ -14180,7 +14192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="99" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:41" ns3:dyDescent="0.25">
       <c r="A99" s="2">
         <v>94</v>
       </c>
@@ -14305,7 +14317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="100" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:41" ns3:dyDescent="0.25">
       <c r="A100" s="2">
         <v>95</v>
       </c>
@@ -14430,7 +14442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="101" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:41" ns3:dyDescent="0.25">
       <c r="A101" s="2">
         <v>96</v>
       </c>
@@ -14555,7 +14567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="102" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:41" ns3:dyDescent="0.25">
       <c r="A102" s="2">
         <v>97</v>
       </c>
@@ -14680,7 +14692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="103" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:41" ns3:dyDescent="0.25">
       <c r="A103" s="2">
         <v>98</v>
       </c>
@@ -14805,7 +14817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="104" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:41" ns3:dyDescent="0.25">
       <c r="A104" s="2">
         <v>99</v>
       </c>
@@ -14930,7 +14942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="105" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:41" ns3:dyDescent="0.25">
       <c r="A105" s="2">
         <v>100</v>
       </c>
@@ -15055,7 +15067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="106" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:41" ns3:dyDescent="0.25">
       <c r="A106" s="2">
         <v>101</v>
       </c>
@@ -15180,7 +15192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="107" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:41" ns3:dyDescent="0.25">
       <c r="A107" s="2">
         <v>102</v>
       </c>
@@ -15305,7 +15317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="108" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:41" ns3:dyDescent="0.25">
       <c r="A108" s="2">
         <v>103</v>
       </c>
@@ -15430,7 +15442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="109" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:41" ns3:dyDescent="0.25">
       <c r="A109" s="2">
         <v>104</v>
       </c>
@@ -15555,7 +15567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="110" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:41" ns3:dyDescent="0.25">
       <c r="A110" s="2">
         <v>105</v>
       </c>
@@ -15680,7 +15692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="111" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:41" ns3:dyDescent="0.25">
       <c r="A111" s="2">
         <v>106</v>
       </c>
@@ -15805,7 +15817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="112" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:41" ns3:dyDescent="0.25">
       <c r="A112" s="2">
         <v>107</v>
       </c>
@@ -15930,7 +15942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="113" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:41" ns3:dyDescent="0.25">
       <c r="A113" s="2">
         <v>108</v>
       </c>
@@ -16055,7 +16067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="114" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:41" ns3:dyDescent="0.25">
       <c r="A114" s="2">
         <v>109</v>
       </c>
@@ -16180,7 +16192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="115" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:41" ns3:dyDescent="0.25">
       <c r="A115" s="2">
         <v>110</v>
       </c>
@@ -16305,7 +16317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="116" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:41" ns3:dyDescent="0.25">
       <c r="A116" s="2">
         <v>111</v>
       </c>
@@ -16430,7 +16442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="117" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:41" ns3:dyDescent="0.25">
       <c r="A117" s="2">
         <v>112</v>
       </c>
@@ -16555,7 +16567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="118" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:41" ns3:dyDescent="0.25">
       <c r="A118" s="2">
         <v>113</v>
       </c>
@@ -16680,7 +16692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="119" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:41" ns3:dyDescent="0.25">
       <c r="A119" s="2">
         <v>114</v>
       </c>
@@ -16805,7 +16817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="120" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:41" ns3:dyDescent="0.25">
       <c r="A120" s="2">
         <v>115</v>
       </c>
@@ -16930,7 +16942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="121" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:41" ns3:dyDescent="0.25">
       <c r="A121" s="2">
         <v>116</v>
       </c>
@@ -17055,7 +17067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="122" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:41" ns3:dyDescent="0.25">
       <c r="A122" s="2">
         <v>117</v>
       </c>
@@ -17180,7 +17192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="123" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:41" ns3:dyDescent="0.25">
       <c r="A123" s="2">
         <v>118</v>
       </c>
@@ -17305,7 +17317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="124" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:41" ns3:dyDescent="0.25">
       <c r="A124" s="2">
         <v>119</v>
       </c>
@@ -17430,7 +17442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="125" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:41" ns3:dyDescent="0.25">
       <c r="A125" s="2">
         <v>120</v>
       </c>
@@ -17555,7 +17567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="126" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:41" ns3:dyDescent="0.25">
       <c r="A126" s="2">
         <v>121</v>
       </c>
@@ -17680,7 +17692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="127" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:41" ns3:dyDescent="0.25">
       <c r="A127" s="2">
         <v>122</v>
       </c>
@@ -17805,7 +17817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="128" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:41" ns3:dyDescent="0.25">
       <c r="A128" s="2">
         <v>123</v>
       </c>
@@ -17930,7 +17942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="129" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:41" ns3:dyDescent="0.25">
       <c r="A129" s="2">
         <v>124</v>
       </c>
@@ -18055,7 +18067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="130" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:41" ns3:dyDescent="0.25">
       <c r="A130" s="2">
         <v>125</v>
       </c>
@@ -18180,7 +18192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="131" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:41" ns3:dyDescent="0.25">
       <c r="A131" s="2">
         <v>126</v>
       </c>
@@ -18305,7 +18317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="132" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:41" ns3:dyDescent="0.25">
       <c r="A132" s="2">
         <v>127</v>
       </c>
@@ -18430,7 +18442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="133" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:41" ns3:dyDescent="0.25">
       <c r="A133" s="2">
         <v>128</v>
       </c>
@@ -18555,7 +18567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="134" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:41" ns3:dyDescent="0.25">
       <c r="A134" s="2">
         <v>129</v>
       </c>
@@ -18680,7 +18692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="135" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:41" ns3:dyDescent="0.25">
       <c r="A135" s="2">
         <v>130</v>
       </c>
@@ -18805,7 +18817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="136" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:41" ns3:dyDescent="0.25">
       <c r="A136" s="2">
         <v>131</v>
       </c>
@@ -18930,7 +18942,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="137" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:41" ns3:dyDescent="0.25">
       <c r="A137" s="2">
         <v>132</v>
       </c>
@@ -19055,7 +19067,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="138" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:41" ns3:dyDescent="0.25">
       <c r="A138" s="2">
         <v>133</v>
       </c>
@@ -19180,7 +19192,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="139" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:41" ns3:dyDescent="0.25">
       <c r="A139" s="2">
         <v>134</v>
       </c>
@@ -19305,7 +19317,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="140" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:41" ns3:dyDescent="0.25">
       <c r="A140" s="2">
         <v>135</v>
       </c>
@@ -19430,7 +19442,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="141" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:41" ns3:dyDescent="0.25">
       <c r="A141" s="2">
         <v>136</v>
       </c>
@@ -19555,7 +19567,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="142" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:41" ns3:dyDescent="0.25">
       <c r="A142" s="2">
         <v>137</v>
       </c>
@@ -19680,7 +19692,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="143" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:41" ns3:dyDescent="0.25">
       <c r="A143" s="2">
         <v>138</v>
       </c>
@@ -19805,7 +19817,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="144" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:41" ns3:dyDescent="0.25">
       <c r="A144" s="2">
         <v>139</v>
       </c>
@@ -19930,7 +19942,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="145" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:41" ns3:dyDescent="0.25">
       <c r="A145" s="2">
         <v>140</v>
       </c>
@@ -20055,7 +20067,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="146" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:41" ns3:dyDescent="0.25">
       <c r="A146" s="2">
         <v>141</v>
       </c>
@@ -20180,7 +20192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="147" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:41" ns3:dyDescent="0.25">
       <c r="A147" s="2">
         <v>142</v>
       </c>
@@ -20305,7 +20317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="148" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:41" ns3:dyDescent="0.25">
       <c r="A148" s="2">
         <v>143</v>
       </c>
@@ -20430,7 +20442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="149" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:41" ns3:dyDescent="0.25">
       <c r="A149" s="2">
         <v>144</v>
       </c>
@@ -20555,7 +20567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="150" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:41" ns3:dyDescent="0.25">
       <c r="A150" s="2">
         <v>145</v>
       </c>
@@ -20680,7 +20692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="151" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:41" ns3:dyDescent="0.25">
       <c r="A151" s="2">
         <v>146</v>
       </c>
@@ -20805,7 +20817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="152" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:41" ns3:dyDescent="0.25">
       <c r="A152" s="2">
         <v>147</v>
       </c>
@@ -20930,7 +20942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="153" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:41" ns3:dyDescent="0.25">
       <c r="A153" s="2">
         <v>148</v>
       </c>
@@ -21055,7 +21067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="154" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:41" ns3:dyDescent="0.25">
       <c r="A154" s="2">
         <v>149</v>
       </c>
@@ -21180,7 +21192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="155" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:41" ns3:dyDescent="0.25">
       <c r="A155" s="2">
         <v>150</v>
       </c>
@@ -21305,7 +21317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="156" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:41" ns3:dyDescent="0.25">
       <c r="A156" s="2">
         <v>151</v>
       </c>
@@ -21430,7 +21442,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="157" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:41" ns3:dyDescent="0.25">
       <c r="A157" s="2">
         <v>152</v>
       </c>
@@ -21555,7 +21567,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="158" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:41" ns3:dyDescent="0.25">
       <c r="A158" s="2">
         <v>153</v>
       </c>
@@ -21680,7 +21692,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="159" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:41" ns3:dyDescent="0.25">
       <c r="A159" s="2">
         <v>154</v>
       </c>
@@ -21805,7 +21817,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="160" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:41" ns3:dyDescent="0.25">
       <c r="A160" s="2">
         <v>155</v>
       </c>
@@ -21930,7 +21942,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="161" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:41" ns3:dyDescent="0.25">
       <c r="A161" s="2">
         <v>156</v>
       </c>
@@ -22055,7 +22067,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="162" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:41" ns3:dyDescent="0.25">
       <c r="A162" s="2">
         <v>157</v>
       </c>
@@ -22180,7 +22192,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="163" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:41" ns3:dyDescent="0.25">
       <c r="A163" s="2">
         <v>158</v>
       </c>
@@ -22305,7 +22317,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="164" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:41" ns3:dyDescent="0.25">
       <c r="A164" s="2">
         <v>159</v>
       </c>
@@ -22430,7 +22442,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="165" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:41" ns3:dyDescent="0.25">
       <c r="A165" s="2">
         <v>160</v>
       </c>
@@ -22555,7 +22567,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="166" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:41" ns3:dyDescent="0.25">
       <c r="A166" s="2">
         <v>161</v>
       </c>
@@ -22680,7 +22692,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="167" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:41" ns3:dyDescent="0.25">
       <c r="A167" s="2">
         <v>162</v>
       </c>
@@ -22805,7 +22817,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="168" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:41" ns3:dyDescent="0.25">
       <c r="A168" s="2">
         <v>163</v>
       </c>
@@ -22930,7 +22942,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="169" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:41" ns3:dyDescent="0.25">
       <c r="A169" s="2">
         <v>164</v>
       </c>
@@ -23055,7 +23067,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="170" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:41" ns3:dyDescent="0.25">
       <c r="A170" s="2">
         <v>165</v>
       </c>
@@ -23180,7 +23192,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="171" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:41" ns3:dyDescent="0.25">
       <c r="A171" s="2">
         <v>166</v>
       </c>
@@ -23305,7 +23317,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="172" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:41" ns3:dyDescent="0.25">
       <c r="A172" s="2">
         <v>167</v>
       </c>
@@ -23430,7 +23442,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="173" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:41" ns3:dyDescent="0.25">
       <c r="A173" s="2">
         <v>168</v>
       </c>
@@ -23555,7 +23567,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="174" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:41" ns3:dyDescent="0.25">
       <c r="A174" s="2">
         <v>169</v>
       </c>
@@ -23680,7 +23692,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="175" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:41" ns3:dyDescent="0.25">
       <c r="A175" s="2">
         <v>170</v>
       </c>
@@ -23805,7 +23817,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="176" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:41" ns3:dyDescent="0.25">
       <c r="A176" s="2">
         <v>171</v>
       </c>
@@ -23930,7 +23942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="177" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:41" ns3:dyDescent="0.25">
       <c r="A177" s="2">
         <v>172</v>
       </c>
@@ -24055,7 +24067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="178" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:41" ns3:dyDescent="0.25">
       <c r="A178" s="2">
         <v>173</v>
       </c>
@@ -24180,7 +24192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="179" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:41" ns3:dyDescent="0.25">
       <c r="A179" s="2">
         <v>174</v>
       </c>
@@ -24305,7 +24317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="180" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:41" ns3:dyDescent="0.25">
       <c r="A180" s="2">
         <v>175</v>
       </c>
@@ -24430,7 +24442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="181" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:41" ns3:dyDescent="0.25">
       <c r="A181" s="2">
         <v>176</v>
       </c>
@@ -24555,7 +24567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="182" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:41" ns3:dyDescent="0.25">
       <c r="A182" s="2">
         <v>177</v>
       </c>
@@ -24680,7 +24692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="183" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:41" ns3:dyDescent="0.25">
       <c r="A183" s="2">
         <v>178</v>
       </c>
@@ -24805,7 +24817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="184" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:41" ns3:dyDescent="0.25">
       <c r="A184" s="2">
         <v>179</v>
       </c>
@@ -24930,7 +24942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="185" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:41" ns3:dyDescent="0.25">
       <c r="A185" s="2">
         <v>180</v>
       </c>
@@ -25055,7 +25067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="186" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:41" ns3:dyDescent="0.25">
       <c r="A186" s="2">
         <v>181</v>
       </c>
@@ -25180,7 +25192,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="187" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:41" ns3:dyDescent="0.25">
       <c r="A187" s="2">
         <v>182</v>
       </c>
@@ -25305,7 +25317,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="188" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:41" ns3:dyDescent="0.25">
       <c r="A188" s="2">
         <v>183</v>
       </c>
@@ -25430,7 +25442,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="189" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:41" ns3:dyDescent="0.25">
       <c r="A189" s="2">
         <v>184</v>
       </c>
@@ -25555,7 +25567,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="190" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:41" ns3:dyDescent="0.25">
       <c r="A190" s="2">
         <v>185</v>
       </c>
@@ -25680,7 +25692,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="191" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:41" ns3:dyDescent="0.25">
       <c r="A191" s="2">
         <v>186</v>
       </c>
@@ -25805,7 +25817,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="192" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:41" ns3:dyDescent="0.25">
       <c r="A192" s="2">
         <v>187</v>
       </c>
@@ -25930,7 +25942,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="193" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:41" ns3:dyDescent="0.25">
       <c r="A193" s="2">
         <v>188</v>
       </c>
@@ -26055,7 +26067,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="194" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:41" ns3:dyDescent="0.25">
       <c r="A194" s="2">
         <v>189</v>
       </c>
@@ -26180,7 +26192,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="195" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:41" ns3:dyDescent="0.25">
       <c r="A195" s="2">
         <v>190</v>
       </c>
@@ -26305,7 +26317,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="196" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:41" ns3:dyDescent="0.25">
       <c r="A196" s="2">
         <v>191</v>
       </c>
@@ -26430,7 +26442,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="197" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:41" ns3:dyDescent="0.25">
       <c r="A197" s="2">
         <v>192</v>
       </c>
@@ -26555,7 +26567,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="198" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:41" ns3:dyDescent="0.25">
       <c r="A198" s="2">
         <v>193</v>
       </c>
@@ -26680,7 +26692,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="199" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:41" ns3:dyDescent="0.25">
       <c r="A199" s="2">
         <v>194</v>
       </c>
@@ -26805,7 +26817,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="200" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:41" ns3:dyDescent="0.25">
       <c r="A200" s="2">
         <v>195</v>
       </c>
@@ -26930,7 +26942,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="201" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:41" ns3:dyDescent="0.25">
       <c r="A201" s="2">
         <v>196</v>
       </c>
@@ -27055,7 +27067,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="202" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:41" ns3:dyDescent="0.25">
       <c r="A202" s="2">
         <v>197</v>
       </c>
@@ -27180,7 +27192,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="203" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:41" ns3:dyDescent="0.25">
       <c r="A203" s="2">
         <v>198</v>
       </c>
@@ -27305,7 +27317,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="204" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:41" ns3:dyDescent="0.25">
       <c r="A204" s="2">
         <v>199</v>
       </c>
@@ -27430,7 +27442,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="205" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:41" ns3:dyDescent="0.25">
       <c r="A205" s="2">
         <v>200</v>
       </c>
@@ -27555,7 +27567,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="206" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:41" ns3:dyDescent="0.25">
       <c r="A206" s="2">
         <v>201</v>
       </c>
@@ -27680,7 +27692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="207" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:41" ns3:dyDescent="0.25">
       <c r="A207" s="2">
         <v>202</v>
       </c>
@@ -27805,7 +27817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="208" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:41" ns3:dyDescent="0.25">
       <c r="A208" s="2">
         <v>203</v>
       </c>
@@ -27930,7 +27942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="209" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:41" ns3:dyDescent="0.25">
       <c r="A209" s="2">
         <v>204</v>
       </c>
@@ -28055,7 +28067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="210" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:41" ns3:dyDescent="0.25">
       <c r="A210" s="2">
         <v>205</v>
       </c>
@@ -28180,7 +28192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="211" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:41" ns3:dyDescent="0.25">
       <c r="A211" s="2">
         <v>206</v>
       </c>
@@ -28305,7 +28317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="212" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:41" ns3:dyDescent="0.25">
       <c r="A212" s="2">
         <v>207</v>
       </c>
@@ -28430,7 +28442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="213" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:41" ns3:dyDescent="0.25">
       <c r="A213" s="2">
         <v>208</v>
       </c>
@@ -28555,7 +28567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="214" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:41" ns3:dyDescent="0.25">
       <c r="A214" s="2">
         <v>209</v>
       </c>
@@ -28680,7 +28692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="215" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:41" ns3:dyDescent="0.25">
       <c r="A215" s="2">
         <v>210</v>
       </c>
@@ -28805,7 +28817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="216" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:41" ns3:dyDescent="0.25">
       <c r="A216" s="2">
         <v>211</v>
       </c>
@@ -28930,7 +28942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="217" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:41" ns3:dyDescent="0.25">
       <c r="A217" s="2">
         <v>212</v>
       </c>
@@ -29055,7 +29067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="218" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:41" ns3:dyDescent="0.25">
       <c r="A218" s="2">
         <v>213</v>
       </c>
@@ -29180,7 +29192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="219" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:41" ns3:dyDescent="0.25">
       <c r="A219" s="2">
         <v>214</v>
       </c>
@@ -29305,7 +29317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="220" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:41" ns3:dyDescent="0.25">
       <c r="A220" s="2">
         <v>215</v>
       </c>
@@ -29430,7 +29442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="221" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:41" ns3:dyDescent="0.25">
       <c r="A221" s="2">
         <v>216</v>
       </c>
@@ -29555,7 +29567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="222" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:41" ns3:dyDescent="0.25">
       <c r="A222" s="2">
         <v>217</v>
       </c>
@@ -29680,7 +29692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="223" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:41" ns3:dyDescent="0.25">
       <c r="A223" s="2">
         <v>218</v>
       </c>
@@ -29805,7 +29817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="224" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:41" ns3:dyDescent="0.25">
       <c r="A224" s="2">
         <v>219</v>
       </c>
@@ -29930,7 +29942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="225" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:41" ns3:dyDescent="0.25">
       <c r="A225" s="2">
         <v>220</v>
       </c>
@@ -30055,7 +30067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="226" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:41" ns3:dyDescent="0.25">
       <c r="A226" s="2">
         <v>221</v>
       </c>
@@ -30180,7 +30192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="227" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:41" ns3:dyDescent="0.25">
       <c r="A227" s="2">
         <v>222</v>
       </c>
@@ -30305,7 +30317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="228" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:41" ns3:dyDescent="0.25">
       <c r="A228" s="2">
         <v>223</v>
       </c>
@@ -30430,7 +30442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="229" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:41" ns3:dyDescent="0.25">
       <c r="A229" s="2">
         <v>224</v>
       </c>
@@ -30555,7 +30567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="230" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:41" ns3:dyDescent="0.25">
       <c r="A230" s="2">
         <v>225</v>
       </c>
@@ -30680,7 +30692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="231" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:41" ns3:dyDescent="0.25">
       <c r="A231" s="2">
         <v>226</v>
       </c>
@@ -30805,7 +30817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="232" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:41" ns3:dyDescent="0.25">
       <c r="A232" s="2">
         <v>227</v>
       </c>
@@ -30930,7 +30942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="233" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:41" ns3:dyDescent="0.25">
       <c r="A233" s="2">
         <v>228</v>
       </c>
@@ -31055,7 +31067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="234" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:41" ns3:dyDescent="0.25">
       <c r="A234" s="2">
         <v>229</v>
       </c>
@@ -31180,7 +31192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="235" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:41" ns3:dyDescent="0.25">
       <c r="A235" s="2">
         <v>230</v>
       </c>
@@ -31305,7 +31317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="236" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:41" ns3:dyDescent="0.25">
       <c r="A236" s="2">
         <v>231</v>
       </c>
@@ -31430,7 +31442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="237" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:41" ns3:dyDescent="0.25">
       <c r="A237" s="2">
         <v>232</v>
       </c>
@@ -31555,7 +31567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="238" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:41" ns3:dyDescent="0.25">
       <c r="A238" s="2">
         <v>233</v>
       </c>
@@ -31680,7 +31692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="239" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:41" ns3:dyDescent="0.25">
       <c r="A239" s="2">
         <v>234</v>
       </c>
@@ -31805,7 +31817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="240" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:41" ns3:dyDescent="0.25">
       <c r="A240" s="2">
         <v>235</v>
       </c>
@@ -31930,7 +31942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="241" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:41" ns3:dyDescent="0.25">
       <c r="A241" s="2">
         <v>236</v>
       </c>
@@ -32055,7 +32067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="242" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:41" ns3:dyDescent="0.25">
       <c r="A242" s="2">
         <v>237</v>
       </c>
@@ -32180,7 +32192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="243" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:41" ns3:dyDescent="0.25">
       <c r="A243" s="2">
         <v>238</v>
       </c>
@@ -32305,7 +32317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="244" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:41" ns3:dyDescent="0.25">
       <c r="A244" s="2">
         <v>239</v>
       </c>
@@ -32430,7 +32442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="245" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:41" ns3:dyDescent="0.25">
       <c r="A245" s="2">
         <v>240</v>
       </c>
@@ -32555,7 +32567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="246" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:41" ns3:dyDescent="0.25">
       <c r="A246" s="2">
         <v>241</v>
       </c>
@@ -32680,7 +32692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="247" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:41" ns3:dyDescent="0.25">
       <c r="A247" s="2">
         <v>242</v>
       </c>
@@ -32805,7 +32817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="248" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:41" ns3:dyDescent="0.25">
       <c r="A248" s="2">
         <v>243</v>
       </c>
@@ -32930,7 +32942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="249" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:41" ns3:dyDescent="0.25">
       <c r="A249" s="2">
         <v>244</v>
       </c>
@@ -33055,7 +33067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="250" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:41" ns3:dyDescent="0.25">
       <c r="A250" s="2">
         <v>245</v>
       </c>
@@ -33180,7 +33192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="251" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:41" ns3:dyDescent="0.25">
       <c r="A251" s="2">
         <v>246</v>
       </c>
@@ -33305,7 +33317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="252" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:41" ns3:dyDescent="0.25">
       <c r="A252" s="2">
         <v>247</v>
       </c>
@@ -33430,7 +33442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="253" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:41" ns3:dyDescent="0.25">
       <c r="A253" s="2">
         <v>248</v>
       </c>
@@ -33555,7 +33567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="254" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:41" ns3:dyDescent="0.25">
       <c r="A254" s="2">
         <v>249</v>
       </c>
@@ -33680,7 +33692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="255" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:41" ns3:dyDescent="0.25">
       <c r="A255" s="2">
         <v>250</v>
       </c>
@@ -33805,7 +33817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="256" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:41" ns3:dyDescent="0.25">
       <c r="A256" s="2">
         <v>251</v>
       </c>
@@ -33930,7 +33942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="257" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:41" ns3:dyDescent="0.25">
       <c r="A257" s="2">
         <v>252</v>
       </c>
@@ -34055,7 +34067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="258" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:41" ns3:dyDescent="0.25">
       <c r="A258" s="2">
         <v>253</v>
       </c>
@@ -34180,7 +34192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="259" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:41" ns3:dyDescent="0.25">
       <c r="A259" s="2">
         <v>254</v>
       </c>
@@ -34305,7 +34317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="260" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:41" ns3:dyDescent="0.25">
       <c r="A260" s="2">
         <v>255</v>
       </c>
@@ -34430,7 +34442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="261" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:41" ns3:dyDescent="0.25">
       <c r="A261" s="2">
         <v>256</v>
       </c>
@@ -34555,7 +34567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="262" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:41" ns3:dyDescent="0.25">
       <c r="A262" s="2">
         <v>257</v>
       </c>
@@ -34680,7 +34692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="263" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:41" ns3:dyDescent="0.25">
       <c r="A263" s="2">
         <v>258</v>
       </c>
@@ -34805,7 +34817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="264" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:41" ns3:dyDescent="0.25">
       <c r="A264" s="2">
         <v>259</v>
       </c>
@@ -34930,7 +34942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="265" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:41" ns3:dyDescent="0.25">
       <c r="A265" s="2">
         <v>260</v>
       </c>
@@ -35055,7 +35067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="266" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:41" ns3:dyDescent="0.25">
       <c r="A266" s="2">
         <v>261</v>
       </c>
@@ -35180,7 +35192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="267" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:41" ns3:dyDescent="0.25">
       <c r="A267" s="2">
         <v>262</v>
       </c>
@@ -35305,7 +35317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="268" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:41" ns3:dyDescent="0.25">
       <c r="A268" s="2">
         <v>263</v>
       </c>
@@ -35430,7 +35442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="269" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:41" ns3:dyDescent="0.25">
       <c r="A269" s="2">
         <v>264</v>
       </c>
@@ -35555,7 +35567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="270" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:41" ns3:dyDescent="0.25">
       <c r="A270" s="2">
         <v>265</v>
       </c>
@@ -35680,7 +35692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="271" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:41" ns3:dyDescent="0.25">
       <c r="A271" s="2">
         <v>266</v>
       </c>
@@ -35805,7 +35817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="272" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:41" ns3:dyDescent="0.25">
       <c r="A272" s="2">
         <v>267</v>
       </c>
@@ -35930,7 +35942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="273" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:41" ns3:dyDescent="0.25">
       <c r="A273" s="2">
         <v>268</v>
       </c>
@@ -36055,7 +36067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="274" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:41" ns3:dyDescent="0.25">
       <c r="A274" s="2">
         <v>269</v>
       </c>
@@ -36180,7 +36192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="275" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:41" ns3:dyDescent="0.25">
       <c r="A275" s="2">
         <v>270</v>
       </c>
@@ -36305,7 +36317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="276" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:41" ns3:dyDescent="0.25">
       <c r="A276" s="2">
         <v>271</v>
       </c>
@@ -36430,7 +36442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="277" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:41" ns3:dyDescent="0.25">
       <c r="A277" s="2">
         <v>272</v>
       </c>
@@ -36555,7 +36567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="278" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:41" ns3:dyDescent="0.25">
       <c r="A278" s="2">
         <v>273</v>
       </c>
@@ -36680,7 +36692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="279" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:41" ns3:dyDescent="0.25">
       <c r="A279" s="2">
         <v>274</v>
       </c>
@@ -36805,7 +36817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="280" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:41" ns3:dyDescent="0.25">
       <c r="A280" s="2">
         <v>275</v>
       </c>
@@ -36930,7 +36942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="281" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:41" ns3:dyDescent="0.25">
       <c r="A281" s="2">
         <v>276</v>
       </c>
@@ -37055,7 +37067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="282" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:41" ns3:dyDescent="0.25">
       <c r="A282" s="2">
         <v>277</v>
       </c>
@@ -37180,7 +37192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="283" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:41" ns3:dyDescent="0.25">
       <c r="A283" s="2">
         <v>278</v>
       </c>
@@ -37305,7 +37317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="284" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:41" ns3:dyDescent="0.25">
       <c r="A284" s="2">
         <v>279</v>
       </c>
@@ -37430,7 +37442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="285" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:41" ns3:dyDescent="0.25">
       <c r="A285" s="2">
         <v>280</v>
       </c>
@@ -37555,7 +37567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="286" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:41" ns3:dyDescent="0.25">
       <c r="A286" s="2">
         <v>281</v>
       </c>
@@ -37680,7 +37692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="287" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:41" ns3:dyDescent="0.25">
       <c r="A287" s="2">
         <v>282</v>
       </c>
@@ -37805,7 +37817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="288" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:41" ns3:dyDescent="0.25">
       <c r="A288" s="2">
         <v>283</v>
       </c>
@@ -37930,7 +37942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="289" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:41" ns3:dyDescent="0.25">
       <c r="A289" s="2">
         <v>284</v>
       </c>
@@ -38055,7 +38067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="290" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:41" ns3:dyDescent="0.25">
       <c r="A290" s="2">
         <v>285</v>
       </c>
@@ -38180,7 +38192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="291" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:41" ns3:dyDescent="0.25">
       <c r="A291" s="2">
         <v>286</v>
       </c>
@@ -38305,7 +38317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="292" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:41" ns3:dyDescent="0.25">
       <c r="A292" s="2">
         <v>287</v>
       </c>
@@ -38430,7 +38442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="293" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:41" ns3:dyDescent="0.25">
       <c r="A293" s="2">
         <v>288</v>
       </c>
@@ -38555,7 +38567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="294" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:41" ns3:dyDescent="0.25">
       <c r="A294" s="2">
         <v>289</v>
       </c>
@@ -38680,7 +38692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="295" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:41" ns3:dyDescent="0.25">
       <c r="A295" s="2">
         <v>290</v>
       </c>
@@ -38805,7 +38817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="296" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:41" ns3:dyDescent="0.25">
       <c r="A296" s="2">
         <v>291</v>
       </c>
@@ -38930,7 +38942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="297" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:41" ns3:dyDescent="0.25">
       <c r="A297" s="2">
         <v>292</v>
       </c>
@@ -39055,7 +39067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="298" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:41" ns3:dyDescent="0.25">
       <c r="A298" s="2">
         <v>293</v>
       </c>
@@ -39180,7 +39192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="299" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:41" ns3:dyDescent="0.25">
       <c r="A299" s="2">
         <v>294</v>
       </c>
@@ -39305,7 +39317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="300" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:41" ns3:dyDescent="0.25">
       <c r="A300" s="2">
         <v>295</v>
       </c>
@@ -39430,7 +39442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="301" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:41" ns3:dyDescent="0.25">
       <c r="A301" s="2">
         <v>296</v>
       </c>
@@ -39555,7 +39567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="302" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:41" ns3:dyDescent="0.25">
       <c r="A302" s="2">
         <v>297</v>
       </c>
@@ -39680,7 +39692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="303" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:41" ns3:dyDescent="0.25">
       <c r="A303" s="2">
         <v>298</v>
       </c>
@@ -39805,7 +39817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="304" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:41" ns3:dyDescent="0.25">
       <c r="A304" s="2">
         <v>299</v>
       </c>
@@ -39930,7 +39942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="305" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:41" ns3:dyDescent="0.25">
       <c r="A305" s="2">
         <v>300</v>
       </c>
@@ -40055,7 +40067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="306" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:41" ns3:dyDescent="0.25">
       <c r="A306" s="2">
         <v>301</v>
       </c>
@@ -40180,7 +40192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="307" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:41" ns3:dyDescent="0.25">
       <c r="A307" s="2">
         <v>302</v>
       </c>
@@ -40305,7 +40317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="308" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:41" ns3:dyDescent="0.25">
       <c r="A308" s="2">
         <v>303</v>
       </c>
@@ -40430,7 +40442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="309" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:41" ns3:dyDescent="0.25">
       <c r="A309" s="2">
         <v>304</v>
       </c>
@@ -40555,7 +40567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="310" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:41" ns3:dyDescent="0.25">
       <c r="A310" s="2">
         <v>305</v>
       </c>
@@ -40680,7 +40692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="311" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:41" ns3:dyDescent="0.25">
       <c r="A311" s="2">
         <v>306</v>
       </c>
@@ -40805,7 +40817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="312" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:41" ns3:dyDescent="0.25">
       <c r="A312" s="2">
         <v>307</v>
       </c>
@@ -40930,7 +40942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="313" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:41" ns3:dyDescent="0.25">
       <c r="A313" s="2">
         <v>308</v>
       </c>
@@ -41055,7 +41067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="314" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:41" ns3:dyDescent="0.25">
       <c r="A314" s="2">
         <v>309</v>
       </c>
@@ -41180,7 +41192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="315" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:41" ns3:dyDescent="0.25">
       <c r="A315" s="2">
         <v>310</v>
       </c>
@@ -41305,7 +41317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="316" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:41" ns3:dyDescent="0.25">
       <c r="A316" s="2">
         <v>311</v>
       </c>
@@ -41430,7 +41442,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="317" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:41" ns3:dyDescent="0.25">
       <c r="A317" s="2">
         <v>312</v>
       </c>
@@ -41555,7 +41567,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="318" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:41" ns3:dyDescent="0.25">
       <c r="A318" s="2">
         <v>313</v>
       </c>
@@ -41680,7 +41692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="319" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:41" ns3:dyDescent="0.25">
       <c r="A319" s="2">
         <v>314</v>
       </c>
@@ -41805,7 +41817,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="320" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:41" ns3:dyDescent="0.25">
       <c r="A320" s="2">
         <v>315</v>
       </c>
@@ -41930,7 +41942,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="321" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:41" ns3:dyDescent="0.25">
       <c r="A321" s="2">
         <v>316</v>
       </c>
@@ -42055,7 +42067,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="322" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:41" ns3:dyDescent="0.25">
       <c r="A322" s="2">
         <v>317</v>
       </c>
@@ -42180,7 +42192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="323" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:41" ns3:dyDescent="0.25">
       <c r="A323" s="2">
         <v>318</v>
       </c>
@@ -42305,7 +42317,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="324" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:41" ns3:dyDescent="0.25">
       <c r="A324" s="2">
         <v>319</v>
       </c>
@@ -42428,12 +42440,137 @@
       </c>
       <c r="AO324" s="5">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:42" ns3:dyDescent="0.25">
+      <c r="A325">
+        <v>320</v>
+      </c>
+      <c r="B325">
+        <v>63</v>
+      </c>
+      <c r="C325">
+        <v>3</v>
+      </c>
+      <c r="D325" t="s">
+        <v>490</v>
+      </c>
+      <c r="E325" t="s">
+        <v>491</v>
+      </c>
+      <c r="F325">
+        <v>1</v>
+      </c>
+      <c r="G325">
+        <v>8</v>
+      </c>
+      <c r="H325">
+        <v>1400</v>
+      </c>
+      <c r="I325">
+        <v>180</v>
+      </c>
+      <c r="J325">
+        <v>180</v>
+      </c>
+      <c r="K325">
+        <v>0</v>
+      </c>
+      <c r="L325">
+        <v>0</v>
+      </c>
+      <c r="M325">
+        <v>100</v>
+      </c>
+      <c r="N325">
+        <v>0</v>
+      </c>
+      <c r="O325">
+        <v>-1</v>
+      </c>
+      <c r="P325">
+        <v>-1</v>
+      </c>
+      <c r="Q325">
+        <v>2</v>
+      </c>
+      <c r="R325">
+        <v>160</v>
+      </c>
+      <c r="S325">
+        <v>160</v>
+      </c>
+      <c r="T325">
+        <v>68</v>
+      </c>
+      <c r="U325">
+        <v>82</v>
+      </c>
+      <c r="V325">
+        <v>58</v>
+      </c>
+      <c r="W325">
+        <v>0</v>
+      </c>
+      <c r="X325">
+        <v>0</v>
+      </c>
+      <c r="Y325">
+        <v>0</v>
+      </c>
+      <c r="Z325">
+        <v>10</v>
+      </c>
+      <c r="AA325">
+        <v>20</v>
+      </c>
+      <c r="AB325">
+        <v>86</v>
+      </c>
+      <c r="AC325">
+        <v>0</v>
+      </c>
+      <c r="AD325">
+        <v>20</v>
+      </c>
+      <c r="AE325">
+        <v>10</v>
+      </c>
+      <c r="AF325">
+        <v>35</v>
+      </c>
+      <c r="AG325">
+        <v>70</v>
+      </c>
+      <c r="AH325">
+        <v>0</v>
+      </c>
+      <c r="AI325">
+        <v>0</v>
+      </c>
+      <c r="AJ325">
+        <v>0</v>
+      </c>
+      <c r="AK325">
+        <v>85</v>
+      </c>
+      <c r="AL325">
+        <v>-1</v>
+      </c>
+      <c r="AM325">
+        <v>0</v>
+      </c>
+      <c r="AN325" t="s">
+        <v>492</v>
+      </c>
+      <c r="AO325" t="s">
+        <v>493</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" ns4:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/jyx2/Assets/Mods/jshyl/Configs/人物.xlsx
+++ b/jyx2/Assets/Mods/jshyl/Configs/人物.xlsx
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -1145,16 +1145,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0</v>
+        <v>999999</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>38</v>
+        <v>9999</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>38</v>
+        <v>999</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
         <v>100</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>-1</v>
@@ -1175,77 +1175,77 @@
         <v>-1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>26</v>
+        <v>9999</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>26</v>
+        <v>999</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>27</v>
+        <v>999</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>27</v>
+        <v>999</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>27</v>
+        <v>999</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>30</v>
+        <v>999</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>30</v>
+        <v>999</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>23</v>
+        <v>999</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>25</v>
+        <v>999</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>30</v>
+        <v>999</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>28</v>
+        <v>999</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>26</v>
+        <v>999</v>
       </c>
       <c r="AD5" s="2" t="n">
-        <v>24</v>
+        <v>999</v>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>25</v>
+        <v>999</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="AG5" s="2" t="n">
-        <v>50</v>
+        <v>999</v>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="AI5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="AL5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="AM5" s="2" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="AN5" s="5" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>1,900|25,900|30,900|57,900|58,900|61,900|87,900|92,900|29,900|205,900</t>
         </is>
       </c>
       <c r="AO5" s="5" t="inlineStr">
@@ -43474,1836 +43474,1836 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="n">
+      <c r="A326" s="0" t="n">
         <v>321</v>
       </c>
-      <c r="B326" t="n">
+      <c r="B326" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="C326" t="n">
+      <c r="C326" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D326" t="inlineStr">
+      <c r="D326" s="0" t="inlineStr">
         <is>
           <t>觉远</t>
         </is>
       </c>
-      <c r="E326" t="inlineStr">
+      <c r="E326" s="0" t="inlineStr">
         <is>
           <t>少林高僧</t>
         </is>
       </c>
-      <c r="F326" t="n">
-        <v>0</v>
-      </c>
-      <c r="G326" t="n">
+      <c r="F326" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G326" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="H326" t="n">
+      <c r="H326" s="0" t="n">
         <v>12000</v>
       </c>
-      <c r="I326" t="n">
+      <c r="I326" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="J326" t="n">
+      <c r="J326" s="0" t="n">
         <v>260</v>
       </c>
-      <c r="K326" t="n">
-        <v>0</v>
-      </c>
-      <c r="L326" t="n">
-        <v>0</v>
-      </c>
-      <c r="M326" t="n">
+      <c r="K326" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L326" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M326" s="0" t="n">
         <v>450</v>
       </c>
-      <c r="N326" t="n">
-        <v>0</v>
-      </c>
-      <c r="O326" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P326" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q326" t="n">
+      <c r="N326" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O326" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P326" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q326" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="R326" t="n">
+      <c r="R326" s="0" t="n">
         <v>120</v>
       </c>
-      <c r="S326" t="n">
+      <c r="S326" s="0" t="n">
         <v>120</v>
       </c>
-      <c r="T326" t="n">
+      <c r="T326" s="0" t="n">
         <v>72</v>
       </c>
-      <c r="U326" t="n">
+      <c r="U326" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="V326" t="n">
+      <c r="V326" s="0" t="n">
         <v>82</v>
       </c>
-      <c r="W326" t="n">
-        <v>0</v>
-      </c>
-      <c r="X326" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y326" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z326" t="n">
+      <c r="W326" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X326" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y326" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z326" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="AA326" t="n">
+      <c r="AA326" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="AB326" t="n">
+      <c r="AB326" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="AC326" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD326" t="n">
+      <c r="AC326" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD326" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="AE326" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF326" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG326" t="n">
+      <c r="AE326" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF326" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG326" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="AH326" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI326" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ326" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK326" t="n">
+      <c r="AH326" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI326" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ326" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK326" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="AL326" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM326" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN326" t="inlineStr">
+      <c r="AL326" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM326" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN326" s="0" t="inlineStr">
         <is>
           <t>1,350</t>
         </is>
       </c>
-      <c r="AO326" t="n">
+      <c r="AO326" s="0" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="n">
+      <c r="A327" s="0" t="n">
         <v>322</v>
       </c>
-      <c r="B327" t="n">
+      <c r="B327" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="C327" t="n">
+      <c r="C327" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D327" t="inlineStr">
+      <c r="D327" s="0" t="inlineStr">
         <is>
           <t>何足道</t>
         </is>
       </c>
-      <c r="E327" t="inlineStr">
+      <c r="E327" s="0" t="inlineStr">
         <is>
           <t>昆仑三圣</t>
         </is>
       </c>
-      <c r="F327" t="n">
-        <v>0</v>
-      </c>
-      <c r="G327" t="n">
+      <c r="F327" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G327" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="H327" t="n">
+      <c r="H327" s="0" t="n">
         <v>16250</v>
       </c>
-      <c r="I327" t="n">
+      <c r="I327" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="J327" t="n">
+      <c r="J327" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="K327" t="n">
-        <v>0</v>
-      </c>
-      <c r="L327" t="n">
-        <v>0</v>
-      </c>
-      <c r="M327" t="n">
+      <c r="K327" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L327" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M327" s="0" t="n">
         <v>500</v>
       </c>
-      <c r="N327" t="n">
-        <v>0</v>
-      </c>
-      <c r="O327" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P327" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q327" t="n">
+      <c r="N327" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O327" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P327" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q327" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="R327" t="n">
+      <c r="R327" s="0" t="n">
         <v>110</v>
       </c>
-      <c r="S327" t="n">
+      <c r="S327" s="0" t="n">
         <v>110</v>
       </c>
-      <c r="T327" t="n">
+      <c r="T327" s="0" t="n">
         <v>78</v>
       </c>
-      <c r="U327" t="n">
+      <c r="U327" s="0" t="n">
         <v>68</v>
       </c>
-      <c r="V327" t="n">
+      <c r="V327" s="0" t="n">
         <v>78</v>
       </c>
-      <c r="W327" t="n">
-        <v>0</v>
-      </c>
-      <c r="X327" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y327" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z327" t="n">
+      <c r="W327" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X327" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y327" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z327" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="AA327" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB327" t="n">
+      <c r="AA327" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB327" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="AC327" t="n">
+      <c r="AC327" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="AD327" t="n">
+      <c r="AD327" s="0" t="n">
         <v>82</v>
       </c>
-      <c r="AE327" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF327" t="n">
+      <c r="AE327" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF327" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="AG327" t="n">
+      <c r="AG327" s="0" t="n">
         <v>55</v>
       </c>
-      <c r="AH327" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI327" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ327" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK327" t="n">
+      <c r="AH327" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI327" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ327" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK327" s="0" t="n">
         <v>78</v>
       </c>
-      <c r="AL327" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM327" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN327" t="inlineStr">
+      <c r="AL327" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM327" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN327" s="0" t="inlineStr">
         <is>
           <t>1,350</t>
         </is>
       </c>
-      <c r="AO327" t="n">
+      <c r="AO327" s="0" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="n">
+      <c r="A328" s="0" t="n">
         <v>323</v>
       </c>
-      <c r="B328" t="n">
+      <c r="B328" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="C328" t="n">
+      <c r="C328" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="D328" t="inlineStr">
+      <c r="D328" s="0" t="inlineStr">
         <is>
           <t>白猿</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr">
+      <c r="E328" s="0" t="inlineStr">
         <is>
           <t>白公公</t>
         </is>
       </c>
-      <c r="F328" t="n">
-        <v>0</v>
-      </c>
-      <c r="G328" t="n">
+      <c r="F328" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G328" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="H328" t="n">
+      <c r="H328" s="0" t="n">
         <v>9250</v>
       </c>
-      <c r="I328" t="n">
+      <c r="I328" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="J328" t="n">
+      <c r="J328" s="0" t="n">
         <v>340</v>
       </c>
-      <c r="K328" t="n">
-        <v>0</v>
-      </c>
-      <c r="L328" t="n">
-        <v>0</v>
-      </c>
-      <c r="M328" t="n">
-        <v>0</v>
-      </c>
-      <c r="N328" t="n">
-        <v>0</v>
-      </c>
-      <c r="O328" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P328" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q328" t="n">
+      <c r="K328" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L328" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M328" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N328" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O328" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P328" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q328" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="R328" t="n">
+      <c r="R328" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="S328" t="n">
+      <c r="S328" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="T328" t="n">
+      <c r="T328" s="0" t="n">
         <v>85</v>
       </c>
-      <c r="U328" t="n">
+      <c r="U328" s="0" t="n">
         <v>78</v>
       </c>
-      <c r="V328" t="n">
+      <c r="V328" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="W328" t="n">
-        <v>0</v>
-      </c>
-      <c r="X328" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y328" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z328" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA328" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB328" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC328" t="n">
+      <c r="W328" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X328" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y328" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z328" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA328" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB328" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC328" s="0" t="n">
         <v>80</v>
       </c>
-      <c r="AD328" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE328" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF328" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG328" t="n">
+      <c r="AD328" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE328" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF328" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG328" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="AH328" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI328" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ328" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK328" t="n">
+      <c r="AH328" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI328" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ328" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK328" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="AL328" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM328" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN328" t="inlineStr">
+      <c r="AL328" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM328" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN328" s="0" t="inlineStr">
         <is>
           <t>1,250</t>
         </is>
       </c>
-      <c r="AO328" t="n">
+      <c r="AO328" s="0" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="n">
+      <c r="A329" s="0" t="n">
         <v>324</v>
       </c>
-      <c r="B329" t="n">
+      <c r="B329" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="C329" t="n">
+      <c r="C329" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D329" t="inlineStr">
+      <c r="D329" s="0" t="inlineStr">
         <is>
           <t>无相</t>
         </is>
       </c>
-      <c r="E329" t="inlineStr">
+      <c r="E329" s="0" t="inlineStr">
         <is>
           <t>西域僧</t>
         </is>
       </c>
-      <c r="F329" t="n">
-        <v>0</v>
-      </c>
-      <c r="G329" t="n">
+      <c r="F329" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G329" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="H329" t="n">
+      <c r="H329" s="0" t="n">
         <v>3850</v>
       </c>
-      <c r="I329" t="n">
+      <c r="I329" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="J329" t="n">
+      <c r="J329" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="K329" t="n">
-        <v>0</v>
-      </c>
-      <c r="L329" t="n">
-        <v>0</v>
-      </c>
-      <c r="M329" t="n">
+      <c r="K329" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L329" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M329" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="N329" t="n">
-        <v>0</v>
-      </c>
-      <c r="O329" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P329" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q329" t="n">
+      <c r="N329" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O329" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P329" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q329" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="R329" t="n">
+      <c r="R329" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="S329" t="n">
+      <c r="S329" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="T329" t="n">
+      <c r="T329" s="0" t="n">
         <v>62</v>
       </c>
-      <c r="U329" t="n">
+      <c r="U329" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="V329" t="n">
+      <c r="V329" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="W329" t="n">
-        <v>0</v>
-      </c>
-      <c r="X329" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y329" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z329" t="n">
+      <c r="W329" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X329" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y329" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z329" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="AA329" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB329" t="n">
+      <c r="AA329" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB329" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="AC329" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD329" t="n">
+      <c r="AC329" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD329" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="AE329" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF329" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG329" t="n">
+      <c r="AE329" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF329" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG329" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="AH329" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI329" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ329" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK329" t="n">
+      <c r="AH329" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI329" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ329" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK329" s="0" t="n">
         <v>55</v>
       </c>
-      <c r="AL329" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM329" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN329" t="inlineStr">
+      <c r="AL329" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM329" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN329" s="0" t="inlineStr">
         <is>
           <t>1,250</t>
         </is>
       </c>
-      <c r="AO329" t="n">
+      <c r="AO329" s="0" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="n">
+      <c r="A330" s="0" t="n">
         <v>325</v>
       </c>
-      <c r="B330" t="n">
+      <c r="B330" s="0" t="n">
         <v>64</v>
       </c>
-      <c r="C330" t="n">
+      <c r="C330" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D330" t="inlineStr">
+      <c r="D330" s="0" t="inlineStr">
         <is>
           <t>无色</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr">
+      <c r="E330" s="0" t="inlineStr">
         <is>
           <t>西域僧</t>
         </is>
       </c>
-      <c r="F330" t="n">
-        <v>0</v>
-      </c>
-      <c r="G330" t="n">
+      <c r="F330" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G330" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="H330" t="n">
+      <c r="H330" s="0" t="n">
         <v>3850</v>
       </c>
-      <c r="I330" t="n">
+      <c r="I330" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="J330" t="n">
+      <c r="J330" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="K330" t="n">
-        <v>0</v>
-      </c>
-      <c r="L330" t="n">
-        <v>0</v>
-      </c>
-      <c r="M330" t="n">
+      <c r="K330" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L330" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M330" s="0" t="n">
         <v>320</v>
       </c>
-      <c r="N330" t="n">
-        <v>0</v>
-      </c>
-      <c r="O330" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P330" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q330" t="n">
+      <c r="N330" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O330" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P330" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q330" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="R330" t="n">
+      <c r="R330" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="S330" t="n">
+      <c r="S330" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="T330" t="n">
+      <c r="T330" s="0" t="n">
         <v>62</v>
       </c>
-      <c r="U330" t="n">
+      <c r="U330" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="V330" t="n">
+      <c r="V330" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="W330" t="n">
-        <v>0</v>
-      </c>
-      <c r="X330" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y330" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z330" t="n">
+      <c r="W330" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X330" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y330" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z330" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="AA330" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB330" t="n">
+      <c r="AA330" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB330" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="AC330" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD330" t="n">
+      <c r="AC330" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD330" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="AE330" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF330" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG330" t="n">
+      <c r="AE330" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF330" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG330" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="AH330" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI330" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ330" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK330" t="n">
+      <c r="AH330" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI330" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ330" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK330" s="0" t="n">
         <v>55</v>
       </c>
-      <c r="AL330" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM330" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN330" t="inlineStr">
+      <c r="AL330" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM330" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN330" s="0" t="inlineStr">
         <is>
           <t>1,250</t>
         </is>
       </c>
-      <c r="AO330" t="n">
+      <c r="AO330" s="0" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="n">
+      <c r="A331" s="0" t="n">
         <v>326</v>
       </c>
-      <c r="B331" t="n">
+      <c r="B331" s="0" t="n">
         <v>71</v>
       </c>
-      <c r="C331" t="n">
+      <c r="C331" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D331" t="inlineStr">
+      <c r="D331" s="0" t="inlineStr">
         <is>
           <t>尹克西</t>
         </is>
       </c>
-      <c r="E331" t="inlineStr">
+      <c r="E331" s="0" t="inlineStr">
         <is>
           <t>西域高手</t>
         </is>
       </c>
-      <c r="F331" t="n">
-        <v>0</v>
-      </c>
-      <c r="G331" t="n">
+      <c r="F331" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G331" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="H331" t="n">
+      <c r="H331" s="0" t="n">
         <v>6350</v>
       </c>
-      <c r="I331" t="n">
+      <c r="I331" s="0" t="n">
         <v>230</v>
       </c>
-      <c r="J331" t="n">
+      <c r="J331" s="0" t="n">
         <v>230</v>
       </c>
-      <c r="K331" t="n">
-        <v>0</v>
-      </c>
-      <c r="L331" t="n">
-        <v>0</v>
-      </c>
-      <c r="M331" t="n">
+      <c r="K331" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L331" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M331" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="N331" t="n">
-        <v>0</v>
-      </c>
-      <c r="O331" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P331" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q331" t="n">
+      <c r="N331" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O331" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P331" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q331" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="R331" t="n">
+      <c r="R331" s="0" t="n">
         <v>75</v>
       </c>
-      <c r="S331" t="n">
+      <c r="S331" s="0" t="n">
         <v>75</v>
       </c>
-      <c r="T331" t="n">
+      <c r="T331" s="0" t="n">
         <v>68</v>
       </c>
-      <c r="U331" t="n">
+      <c r="U331" s="0" t="n">
         <v>42</v>
       </c>
-      <c r="V331" t="n">
+      <c r="V331" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="W331" t="n">
-        <v>0</v>
-      </c>
-      <c r="X331" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y331" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z331" t="n">
+      <c r="W331" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X331" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y331" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z331" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="AA331" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB331" t="n">
+      <c r="AA331" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB331" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="AC331" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD331" t="n">
+      <c r="AC331" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD331" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="AE331" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF331" t="n">
+      <c r="AE331" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF331" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="AG331" t="n">
+      <c r="AG331" s="0" t="n">
         <v>48</v>
       </c>
-      <c r="AH331" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI331" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ331" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK331" t="n">
+      <c r="AH331" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI331" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ331" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK331" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="AL331" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM331" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN331" t="inlineStr">
+      <c r="AL331" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM331" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN331" s="0" t="inlineStr">
         <is>
           <t>1,300</t>
         </is>
       </c>
-      <c r="AO331" t="n">
+      <c r="AO331" s="0" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="n">
+      <c r="A332" s="0" t="n">
         <v>327</v>
       </c>
-      <c r="B332" t="n">
+      <c r="B332" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="C332" t="n">
+      <c r="C332" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D332" t="inlineStr">
+      <c r="D332" s="0" t="inlineStr">
         <is>
           <t>潇湘子</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr">
+      <c r="E332" s="0" t="inlineStr">
         <is>
           <t>湘西高手</t>
         </is>
       </c>
-      <c r="F332" t="n">
-        <v>0</v>
-      </c>
-      <c r="G332" t="n">
+      <c r="F332" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G332" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="H332" t="n">
+      <c r="H332" s="0" t="n">
         <v>6350</v>
       </c>
-      <c r="I332" t="n">
+      <c r="I332" s="0" t="n">
         <v>230</v>
       </c>
-      <c r="J332" t="n">
+      <c r="J332" s="0" t="n">
         <v>230</v>
       </c>
-      <c r="K332" t="n">
-        <v>0</v>
-      </c>
-      <c r="L332" t="n">
-        <v>0</v>
-      </c>
-      <c r="M332" t="n">
+      <c r="K332" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L332" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M332" s="0" t="n">
         <v>360</v>
       </c>
-      <c r="N332" t="n">
-        <v>0</v>
-      </c>
-      <c r="O332" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P332" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q332" t="n">
+      <c r="N332" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O332" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P332" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q332" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="R332" t="n">
+      <c r="R332" s="0" t="n">
         <v>75</v>
       </c>
-      <c r="S332" t="n">
+      <c r="S332" s="0" t="n">
         <v>75</v>
       </c>
-      <c r="T332" t="n">
+      <c r="T332" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="U332" t="n">
+      <c r="U332" s="0" t="n">
         <v>55</v>
       </c>
-      <c r="V332" t="n">
+      <c r="V332" s="0" t="n">
         <v>66</v>
       </c>
-      <c r="W332" t="n">
-        <v>0</v>
-      </c>
-      <c r="X332" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y332" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z332" t="n">
+      <c r="W332" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X332" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y332" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z332" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="AA332" t="n">
+      <c r="AA332" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="AB332" t="n">
+      <c r="AB332" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="AC332" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD332" t="n">
+      <c r="AC332" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD332" s="0" t="n">
         <v>55</v>
       </c>
-      <c r="AE332" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF332" t="n">
+      <c r="AE332" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF332" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="AG332" t="n">
+      <c r="AG332" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="AH332" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI332" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ332" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK332" t="n">
+      <c r="AH332" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI332" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ332" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK332" s="0" t="n">
         <v>62</v>
       </c>
-      <c r="AL332" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM332" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN332" t="inlineStr">
+      <c r="AL332" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM332" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN332" s="0" t="inlineStr">
         <is>
           <t>1,300</t>
         </is>
       </c>
-      <c r="AO332" t="n">
+      <c r="AO332" s="0" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="n">
+      <c r="A333" s="0" t="n">
         <v>328</v>
       </c>
-      <c r="B333" t="n">
+      <c r="B333" s="0" t="n">
         <v>71</v>
       </c>
-      <c r="C333" t="n">
+      <c r="C333" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D333" t="inlineStr">
+      <c r="D333" s="0" t="inlineStr">
         <is>
           <t>西域三僧甲</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr">
+      <c r="E333" s="0" t="inlineStr">
         <is>
           <t>西域三僧</t>
         </is>
       </c>
-      <c r="F333" t="n">
-        <v>0</v>
-      </c>
-      <c r="G333" t="n">
+      <c r="F333" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G333" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H333" t="n">
+      <c r="H333" s="0" t="n">
         <v>3050</v>
       </c>
-      <c r="I333" t="n">
+      <c r="I333" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="J333" t="n">
+      <c r="J333" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="K333" t="n">
-        <v>0</v>
-      </c>
-      <c r="L333" t="n">
-        <v>0</v>
-      </c>
-      <c r="M333" t="n">
+      <c r="K333" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L333" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M333" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="N333" t="n">
-        <v>0</v>
-      </c>
-      <c r="O333" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P333" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q333" t="n">
+      <c r="N333" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O333" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P333" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q333" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="R333" t="n">
+      <c r="R333" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="S333" t="n">
+      <c r="S333" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="T333" t="n">
+      <c r="T333" s="0" t="n">
         <v>58</v>
       </c>
-      <c r="U333" t="n">
+      <c r="U333" s="0" t="n">
         <v>36</v>
       </c>
-      <c r="V333" t="n">
+      <c r="V333" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="W333" t="n">
-        <v>0</v>
-      </c>
-      <c r="X333" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y333" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z333" t="n">
+      <c r="W333" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X333" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y333" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z333" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="AA333" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB333" t="n">
+      <c r="AA333" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB333" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="AC333" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD333" t="n">
+      <c r="AC333" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD333" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="AE333" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF333" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG333" t="n">
+      <c r="AE333" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF333" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG333" s="0" t="n">
         <v>42</v>
       </c>
-      <c r="AH333" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI333" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ333" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK333" t="n">
+      <c r="AH333" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI333" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ333" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK333" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="AL333" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM333" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN333" t="inlineStr">
+      <c r="AL333" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM333" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN333" s="0" t="inlineStr">
         <is>
           <t>1,220</t>
         </is>
       </c>
-      <c r="AO333" t="n">
+      <c r="AO333" s="0" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="n">
+      <c r="A334" s="0" t="n">
         <v>329</v>
       </c>
-      <c r="B334" t="n">
+      <c r="B334" s="0" t="n">
         <v>71</v>
       </c>
-      <c r="C334" t="n">
+      <c r="C334" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D334" t="inlineStr">
+      <c r="D334" s="0" t="inlineStr">
         <is>
           <t>西域三僧乙</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr">
+      <c r="E334" s="0" t="inlineStr">
         <is>
           <t>西域三僧</t>
         </is>
       </c>
-      <c r="F334" t="n">
-        <v>0</v>
-      </c>
-      <c r="G334" t="n">
+      <c r="F334" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G334" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H334" t="n">
+      <c r="H334" s="0" t="n">
         <v>3050</v>
       </c>
-      <c r="I334" t="n">
+      <c r="I334" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="J334" t="n">
+      <c r="J334" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="K334" t="n">
-        <v>0</v>
-      </c>
-      <c r="L334" t="n">
-        <v>0</v>
-      </c>
-      <c r="M334" t="n">
+      <c r="K334" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L334" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M334" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="N334" t="n">
-        <v>0</v>
-      </c>
-      <c r="O334" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P334" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q334" t="n">
+      <c r="N334" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O334" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P334" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q334" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="R334" t="n">
+      <c r="R334" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="S334" t="n">
+      <c r="S334" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="T334" t="n">
+      <c r="T334" s="0" t="n">
         <v>58</v>
       </c>
-      <c r="U334" t="n">
+      <c r="U334" s="0" t="n">
         <v>36</v>
       </c>
-      <c r="V334" t="n">
+      <c r="V334" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="W334" t="n">
-        <v>0</v>
-      </c>
-      <c r="X334" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y334" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z334" t="n">
+      <c r="W334" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X334" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y334" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z334" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="AA334" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB334" t="n">
+      <c r="AA334" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB334" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="AC334" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD334" t="n">
+      <c r="AC334" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD334" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="AE334" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF334" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG334" t="n">
+      <c r="AE334" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF334" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG334" s="0" t="n">
         <v>42</v>
       </c>
-      <c r="AH334" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI334" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ334" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK334" t="n">
+      <c r="AH334" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI334" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ334" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK334" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="AL334" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM334" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN334" t="inlineStr">
+      <c r="AL334" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM334" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN334" s="0" t="inlineStr">
         <is>
           <t>1,220</t>
         </is>
       </c>
-      <c r="AO334" t="n">
+      <c r="AO334" s="0" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="n">
+      <c r="A335" s="0" t="n">
         <v>330</v>
       </c>
-      <c r="B335" t="n">
+      <c r="B335" s="0" t="n">
         <v>71</v>
       </c>
-      <c r="C335" t="n">
+      <c r="C335" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D335" t="inlineStr">
+      <c r="D335" s="0" t="inlineStr">
         <is>
           <t>西域三僧丙</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr">
+      <c r="E335" s="0" t="inlineStr">
         <is>
           <t>西域三僧</t>
         </is>
       </c>
-      <c r="F335" t="n">
-        <v>0</v>
-      </c>
-      <c r="G335" t="n">
+      <c r="F335" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G335" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="H335" t="n">
+      <c r="H335" s="0" t="n">
         <v>3050</v>
       </c>
-      <c r="I335" t="n">
+      <c r="I335" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="J335" t="n">
+      <c r="J335" s="0" t="n">
         <v>190</v>
       </c>
-      <c r="K335" t="n">
-        <v>0</v>
-      </c>
-      <c r="L335" t="n">
-        <v>0</v>
-      </c>
-      <c r="M335" t="n">
+      <c r="K335" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L335" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M335" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="N335" t="n">
-        <v>0</v>
-      </c>
-      <c r="O335" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P335" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q335" t="n">
+      <c r="N335" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O335" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P335" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q335" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="R335" t="n">
+      <c r="R335" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="S335" t="n">
+      <c r="S335" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="T335" t="n">
+      <c r="T335" s="0" t="n">
         <v>58</v>
       </c>
-      <c r="U335" t="n">
+      <c r="U335" s="0" t="n">
         <v>36</v>
       </c>
-      <c r="V335" t="n">
+      <c r="V335" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="W335" t="n">
-        <v>0</v>
-      </c>
-      <c r="X335" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y335" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z335" t="n">
+      <c r="W335" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X335" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y335" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z335" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="AA335" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB335" t="n">
+      <c r="AA335" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB335" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="AC335" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD335" t="n">
+      <c r="AC335" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD335" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="AE335" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF335" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG335" t="n">
+      <c r="AE335" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF335" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG335" s="0" t="n">
         <v>42</v>
       </c>
-      <c r="AH335" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI335" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ335" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK335" t="n">
+      <c r="AH335" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI335" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ335" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK335" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="AL335" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM335" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN335" t="inlineStr">
+      <c r="AL335" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM335" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN335" s="0" t="inlineStr">
         <is>
           <t>1,220</t>
         </is>
       </c>
-      <c r="AO335" t="n">
+      <c r="AO335" s="0" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="n">
+      <c r="A336" s="0" t="n">
         <v>331</v>
       </c>
-      <c r="B336" t="n">
+      <c r="B336" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="C336" t="n">
+      <c r="C336" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D336" t="inlineStr">
+      <c r="D336" s="0" t="inlineStr">
         <is>
           <t>天鸣</t>
         </is>
       </c>
-      <c r="E336" t="inlineStr">
+      <c r="E336" s="0" t="inlineStr">
         <is>
           <t>少林高僧</t>
         </is>
       </c>
-      <c r="F336" t="n">
-        <v>0</v>
-      </c>
-      <c r="G336" t="n">
+      <c r="F336" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G336" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="H336" t="n">
+      <c r="H336" s="0" t="n">
         <v>9250</v>
       </c>
-      <c r="I336" t="n">
+      <c r="I336" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="J336" t="n">
+      <c r="J336" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="K336" t="n">
-        <v>0</v>
-      </c>
-      <c r="L336" t="n">
-        <v>0</v>
-      </c>
-      <c r="M336" t="n">
+      <c r="K336" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L336" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M336" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="N336" t="n">
-        <v>0</v>
-      </c>
-      <c r="O336" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P336" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q336" t="n">
+      <c r="N336" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O336" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P336" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q336" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="R336" t="n">
+      <c r="R336" s="0" t="n">
         <v>85</v>
       </c>
-      <c r="S336" t="n">
+      <c r="S336" s="0" t="n">
         <v>85</v>
       </c>
-      <c r="T336" t="n">
+      <c r="T336" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="U336" t="n">
+      <c r="U336" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="V336" t="n">
+      <c r="V336" s="0" t="n">
         <v>76</v>
       </c>
-      <c r="W336" t="n">
-        <v>0</v>
-      </c>
-      <c r="X336" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y336" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z336" t="n">
+      <c r="W336" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X336" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y336" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z336" s="0" t="n">
         <v>55</v>
       </c>
-      <c r="AA336" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB336" t="n">
+      <c r="AA336" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB336" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="AC336" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD336" t="n">
+      <c r="AC336" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD336" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="AE336" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF336" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG336" t="n">
+      <c r="AE336" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF336" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG336" s="0" t="n">
         <v>58</v>
       </c>
-      <c r="AH336" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI336" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ336" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK336" t="n">
+      <c r="AH336" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI336" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ336" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK336" s="0" t="n">
         <v>68</v>
       </c>
-      <c r="AL336" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM336" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN336" t="inlineStr">
+      <c r="AL336" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM336" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN336" s="0" t="inlineStr">
         <is>
           <t>1,320</t>
         </is>
       </c>
-      <c r="AO336" t="n">
+      <c r="AO336" s="0" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="n">
+      <c r="A337" s="0" t="n">
         <v>332</v>
       </c>
-      <c r="B337" t="n">
+      <c r="B337" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="C337" t="n">
+      <c r="C337" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="D337" t="inlineStr">
+      <c r="D337" s="0" t="inlineStr">
         <is>
           <t>卓不凡</t>
         </is>
       </c>
-      <c r="E337" t="inlineStr">
+      <c r="E337" s="0" t="inlineStr">
         <is>
           <t>剑神</t>
         </is>
       </c>
-      <c r="F337" t="n">
-        <v>0</v>
-      </c>
-      <c r="G337" t="n">
+      <c r="F337" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G337" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="H337" t="n">
+      <c r="H337" s="0" t="n">
         <v>21400</v>
       </c>
-      <c r="I337" t="n">
+      <c r="I337" s="0" t="n">
         <v>520</v>
       </c>
-      <c r="J337" t="n">
+      <c r="J337" s="0" t="n">
         <v>520</v>
       </c>
-      <c r="K337" t="n">
-        <v>0</v>
-      </c>
-      <c r="L337" t="n">
-        <v>0</v>
-      </c>
-      <c r="M337" t="n">
+      <c r="K337" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L337" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M337" s="0" t="n">
         <v>650</v>
       </c>
-      <c r="N337" t="n">
-        <v>0</v>
-      </c>
-      <c r="O337" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P337" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q337" t="n">
+      <c r="N337" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O337" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P337" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q337" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="R337" t="n">
+      <c r="R337" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="S337" t="n">
+      <c r="S337" s="0" t="n">
         <v>160</v>
       </c>
-      <c r="T337" t="n">
+      <c r="T337" s="0" t="n">
         <v>88</v>
       </c>
-      <c r="U337" t="n">
+      <c r="U337" s="0" t="n">
         <v>82</v>
       </c>
-      <c r="V337" t="n">
+      <c r="V337" s="0" t="n">
         <v>84</v>
       </c>
-      <c r="W337" t="n">
-        <v>0</v>
-      </c>
-      <c r="X337" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y337" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z337" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA337" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB337" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC337" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD337" t="n">
+      <c r="W337" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X337" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y337" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z337" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA337" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB337" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC337" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD337" s="0" t="n">
         <v>92</v>
       </c>
-      <c r="AE337" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF337" t="n">
+      <c r="AE337" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF337" s="0" t="n">
         <v>88</v>
       </c>
-      <c r="AG337" t="n">
+      <c r="AG337" s="0" t="n">
         <v>65</v>
       </c>
-      <c r="AH337" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI337" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ337" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK337" t="n">
+      <c r="AH337" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI337" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ337" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK337" s="0" t="n">
         <v>75</v>
       </c>
-      <c r="AL337" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM337" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN337" t="inlineStr">
+      <c r="AL337" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM337" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN337" s="0" t="inlineStr">
         <is>
           <t>1,500</t>
         </is>
       </c>
-      <c r="AO337" t="n">
+      <c r="AO337" s="0" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="n">
+      <c r="A338" s="0" t="n">
         <v>333</v>
       </c>
-      <c r="B338" t="n">
+      <c r="B338" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="C338" t="n">
+      <c r="C338" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D338" t="inlineStr">
+      <c r="D338" s="0" t="inlineStr">
         <is>
           <t>公孙止</t>
         </is>
       </c>
-      <c r="E338" t="inlineStr">
+      <c r="E338" s="0" t="inlineStr">
         <is>
           <t>绝情谷主</t>
         </is>
       </c>
-      <c r="F338" t="n">
-        <v>0</v>
-      </c>
-      <c r="G338" t="n">
+      <c r="F338" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G338" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="H338" t="n">
+      <c r="H338" s="0" t="n">
         <v>28150</v>
       </c>
-      <c r="I338" t="n">
+      <c r="I338" s="0" t="n">
         <v>650</v>
       </c>
-      <c r="J338" t="n">
+      <c r="J338" s="0" t="n">
         <v>650</v>
       </c>
-      <c r="K338" t="n">
-        <v>0</v>
-      </c>
-      <c r="L338" t="n">
-        <v>0</v>
-      </c>
-      <c r="M338" t="n">
+      <c r="K338" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L338" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M338" s="0" t="n">
         <v>720</v>
       </c>
-      <c r="N338" t="n">
-        <v>0</v>
-      </c>
-      <c r="O338" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P338" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q338" t="n">
+      <c r="N338" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O338" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P338" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q338" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="R338" t="n">
+      <c r="R338" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="S338" t="n">
+      <c r="S338" s="0" t="n">
         <v>210</v>
       </c>
-      <c r="T338" t="n">
+      <c r="T338" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="U338" t="n">
+      <c r="U338" s="0" t="n">
         <v>78</v>
       </c>
-      <c r="V338" t="n">
+      <c r="V338" s="0" t="n">
         <v>92</v>
       </c>
-      <c r="W338" t="n">
-        <v>0</v>
-      </c>
-      <c r="X338" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y338" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z338" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA338" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB338" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC338" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD338" t="n">
+      <c r="W338" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X338" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y338" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z338" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA338" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB338" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC338" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD338" s="0" t="n">
         <v>86</v>
       </c>
-      <c r="AE338" t="n">
+      <c r="AE338" s="0" t="n">
         <v>80</v>
       </c>
-      <c r="AF338" t="n">
+      <c r="AF338" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="AG338" t="n">
+      <c r="AG338" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="AH338" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI338" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ338" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK338" t="n">
+      <c r="AH338" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI338" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ338" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK338" s="0" t="n">
         <v>70</v>
       </c>
-      <c r="AL338" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM338" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN338" t="inlineStr">
+      <c r="AL338" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM338" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN338" s="0" t="inlineStr">
         <is>
           <t>1,600</t>
         </is>
       </c>
-      <c r="AO338" t="n">
+      <c r="AO338" s="0" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="n">
+      <c r="A339" s="0" t="n">
         <v>334</v>
       </c>
-      <c r="B339" t="n">
+      <c r="B339" s="0" t="n">
         <v>63</v>
       </c>
-      <c r="C339" t="n">
+      <c r="C339" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="D339" t="inlineStr">
+      <c r="D339" s="0" t="inlineStr">
         <is>
           <t>九天玄女</t>
         </is>
       </c>
-      <c r="E339" t="inlineStr">
+      <c r="E339" s="0" t="inlineStr">
         <is>
           <t>天上玄女</t>
         </is>
       </c>
-      <c r="F339" t="n">
+      <c r="F339" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G339" t="n">
+      <c r="G339" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="H339" t="n">
+      <c r="H339" s="0" t="n">
         <v>-9036</v>
       </c>
-      <c r="I339" t="n">
+      <c r="I339" s="0" t="n">
         <v>900</v>
       </c>
-      <c r="J339" t="n">
+      <c r="J339" s="0" t="n">
         <v>900</v>
       </c>
-      <c r="K339" t="n">
-        <v>0</v>
-      </c>
-      <c r="L339" t="n">
-        <v>0</v>
-      </c>
-      <c r="M339" t="n">
+      <c r="K339" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L339" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M339" s="0" t="n">
         <v>999</v>
       </c>
-      <c r="N339" t="n">
-        <v>0</v>
-      </c>
-      <c r="O339" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P339" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q339" t="n">
+      <c r="N339" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O339" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P339" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q339" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="R339" t="n">
+      <c r="R339" s="0" t="n">
         <v>999</v>
       </c>
-      <c r="S339" t="n">
+      <c r="S339" s="0" t="n">
         <v>999</v>
       </c>
-      <c r="T339" t="n">
+      <c r="T339" s="0" t="n">
         <v>99</v>
       </c>
-      <c r="U339" t="n">
+      <c r="U339" s="0" t="n">
         <v>99</v>
       </c>
-      <c r="V339" t="n">
+      <c r="V339" s="0" t="n">
         <v>99</v>
       </c>
-      <c r="W339" t="n">
-        <v>0</v>
-      </c>
-      <c r="X339" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y339" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z339" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA339" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB339" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC339" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD339" t="n">
+      <c r="W339" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X339" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y339" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z339" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA339" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB339" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC339" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD339" s="0" t="n">
         <v>99</v>
       </c>
-      <c r="AE339" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF339" t="n">
+      <c r="AE339" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF339" s="0" t="n">
         <v>99</v>
       </c>
-      <c r="AG339" t="n">
+      <c r="AG339" s="0" t="n">
         <v>90</v>
       </c>
-      <c r="AH339" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI339" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ339" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK339" t="n">
+      <c r="AH339" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI339" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ339" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK339" s="0" t="n">
         <v>99</v>
       </c>
-      <c r="AL339" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM339" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN339" t="inlineStr">
+      <c r="AL339" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AM339" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN339" s="0" t="inlineStr">
         <is>
           <t>61,900</t>
         </is>
       </c>
-      <c r="AO339" t="n">
+      <c r="AO339" s="0" t="n">
         <v>-1</v>
       </c>
     </row>
